--- a/artfynd/A 29264-2024 artfynd.xlsx
+++ b/artfynd/A 29264-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118393695</v>
+        <v>118393718</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585921</v>
+        <v>585936</v>
       </c>
       <c r="R2" t="n">
-        <v>7059472</v>
+        <v>7059473</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393718</v>
+        <v>118393695</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585936</v>
+        <v>585921</v>
       </c>
       <c r="R4" t="n">
-        <v>7059473</v>
+        <v>7059472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29264-2024 artfynd.xlsx
+++ b/artfynd/A 29264-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118393718</v>
+        <v>118393940</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>97763</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585936</v>
+        <v>585901</v>
       </c>
       <c r="R2" t="n">
-        <v>7059473</v>
+        <v>7059606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393940</v>
+        <v>118393695</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585901</v>
+        <v>585921</v>
       </c>
       <c r="R3" t="n">
-        <v>7059606</v>
+        <v>7059472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393695</v>
+        <v>118393718</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585921</v>
+        <v>585936</v>
       </c>
       <c r="R4" t="n">
-        <v>7059472</v>
+        <v>7059473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29264-2024 artfynd.xlsx
+++ b/artfynd/A 29264-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118393940</v>
       </c>
       <c r="B2" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393695</v>
+        <v>118393718</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585921</v>
+        <v>585936</v>
       </c>
       <c r="R3" t="n">
-        <v>7059472</v>
+        <v>7059473</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393718</v>
+        <v>118393695</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585936</v>
+        <v>585921</v>
       </c>
       <c r="R4" t="n">
-        <v>7059473</v>
+        <v>7059472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29264-2024 artfynd.xlsx
+++ b/artfynd/A 29264-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118393940</v>
+        <v>118393695</v>
       </c>
       <c r="B2" t="n">
-        <v>97770</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585901</v>
+        <v>585921</v>
       </c>
       <c r="R2" t="n">
-        <v>7059606</v>
+        <v>7059472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393718</v>
+        <v>118393940</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585936</v>
+        <v>585901</v>
       </c>
       <c r="R3" t="n">
-        <v>7059473</v>
+        <v>7059606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393695</v>
+        <v>118393718</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585921</v>
+        <v>585936</v>
       </c>
       <c r="R4" t="n">
-        <v>7059472</v>
+        <v>7059473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
